--- a/EKG_Kalite_Yönetim_Sistemi/90_NSA, MPA ve PPQ Hazırlık Araçları/01_Kaynak Form, Kriter ve Kanıt Takibi/EKG-YNT-MTR-06_saha_kaniti_izlenebilirlik_matrisi__excel_duzeni.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/90_NSA, MPA ve PPQ Hazırlık Araçları/01_Kaynak Form, Kriter ve Kanıt Takibi/EKG-YNT-MTR-06_saha_kaniti_izlenebilirlik_matrisi__excel_duzeni.xlsx
@@ -811,7 +811,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-YNT-MTR-06&amp;C&amp;"Arial,Regular"&amp;11Saha Kanıtı İzlenebilirlik Matrisi - Excel Düzeni</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.06.2026 | Revizyon: 09.09.2026
+Revizyon nedeni: Word düzeniyle tutarlı kaynak-revizyon, gerçek kayıt, sorumlu ve sonuç matrisi kuruldu.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>